--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\godkn\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B587FCFA-3109-4970-9B73-79B5F8DF75A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732953B4-E705-472C-A141-93E22D199BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0D5148DB-0F40-4791-8578-71900E8F3673}"/>
   </bookViews>
@@ -237,10 +237,9 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -249,10 +248,7 @@
     <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -657,7 +653,7 @@
     <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -669,7 +665,7 @@
       <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -683,7 +679,7 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <f ca="1">AVERAGE(Table1[Monthly Sales (000)])</f>
         <v>49.416666666666664</v>
       </c>
@@ -692,13 +688,13 @@
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <f ca="1">MEDIAN(Table1[Monthly Sales (000)])</f>
         <v>47.5</v>
       </c>
@@ -707,7 +703,7 @@
       <c r="A5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>44</v>
       </c>
       <c r="D5" t="s">
@@ -716,7 +712,7 @@
       <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <f ca="1">MODE(Table1[Monthly Sales (000)])</f>
         <v>46</v>
       </c>
@@ -725,13 +721,13 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <f>MAX(B4:B15)-MIN(B4:B15)</f>
         <v>29</v>
       </c>
@@ -740,7 +736,7 @@
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>46</v>
       </c>
     </row>
@@ -748,7 +744,7 @@
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>52</v>
       </c>
     </row>
@@ -756,38 +752,36 @@
       <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>47</v>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>45</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <f ca="1">_xlfn.STDEV.S(Table1[Monthly Sales (000)])</f>
         <v>7.6331613054586773</v>
       </c>
@@ -796,13 +790,13 @@
       <c r="A12" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>43</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <f>_xlfn.STDEV.S(B4:B10,B12:B15)</f>
         <v>2.9076701075853588</v>
       </c>
@@ -811,13 +805,13 @@
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>48</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <f ca="1">F11-F12</f>
         <v>4.7254911978733185</v>
       </c>
@@ -826,7 +820,7 @@
       <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>46</v>
       </c>
     </row>
@@ -834,7 +828,7 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>50</v>
       </c>
     </row>
@@ -842,21 +836,21 @@
       <c r="A16" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <f ca="1">SUM(Table1[Monthly Sales (000)])</f>
         <v>593</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -877,169 +871,169 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
     </row>
     <row r="4" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="11"/>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="12"/>
+      <c r="B7" s="10"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="11"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="11"/>
-      <c r="AG11" s="11"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
